--- a/config/Parameterliste.xlsx
+++ b/config/Parameterliste.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="51480" yWindow="2100" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Parameterliste" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,12 +27,12 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
-      <color rgb="00202B30"/>
+      <color rgb="FF202B30"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -46,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00245B68"/>
+        <fgColor rgb="FF245B68"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +74,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -486,7 +485,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -499,7 +498,7 @@
           <t>Settes alltid til Ny</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -512,7 +511,7 @@
           <t>Settes alltid til K5B</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -525,7 +524,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -538,7 +537,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -551,7 +550,7 @@
           <t>Fylles etter regel 2 når én pakke har strengt flertall blant de nærmeste naboene; skal ikke være tom.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -564,7 +563,7 @@
           <t>For allt unntatt kabelbro og trekkerør strekk settes verdi 1</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -577,7 +576,7 @@
           <t>For føringsveier rette strekk brukes m For alt annet stk også fittjngs</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -604,10 +603,14 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Ingen særskilt fagregel angitt</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
+          <t>For OST_CableTray og OST_CableTrayFitting: Når FOB_Merkestreng, FOB_Sekvensnummer eller FOB_Omraade mangler, kjøres C#-forløperen automatisk av Regel 3 før generell utfylling. Den bygger FOB_Merkestreng som FOB_Omraade-FOB_System-FOB_Funksjonskode-NNNN. Manglende område på fitting hentes fra entydig fysisk tilkoblet rett kabelbro; rett kabelbro bruker område fra inneholdende Space. Forløperen behandler alle slike elementer i aktiv modell, ikke bare K5B, og kan endre eksisterende grupper ved duplikater eller sekvensgap. Strømskinner, typefunksjonskode STS og FOB_Status S5 utelates/beskyttes. Kontroller modellomfang før kjøring.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/CableTrayMarkingEngine.cs; CSharpRules/Rule03ParameterFill.cs</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -620,7 +623,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -630,10 +633,14 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Ingen særskilt fagregel angitt</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
+          <t>For OST_CableTray og OST_CableTrayFitting: Når FOB_Omraade, FOB_Sekvensnummer eller FOB_Merkestreng mangler, kjøres C#-forløperen automatisk av Regel 3. Manglende område på rett kabelbro hentes fra inneholdende Space; fitting bruker én entydig verdi fra fysisk tilkoblet rett kabelbro. Motstridende eller manglende kilder logges som uavklart, ikke som --. Forløperen behandler alle slike elementer i aktiv modell, ikke bare K5B; kontroller modellomfang før kjøring.</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/CableTrayMarkingEngine.cs; CSharpRules/Rule03ParameterFill.cs</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -646,9 +653,9 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>FOB_Revisjonsdato</t>
@@ -668,15 +675,19 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FOB_Sekevensnummer</t>
+          <t>FOB_Sekvensnummer</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Ingen særskilt fagregel angitt</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr"/>
+          <t>For OST_CableTray og OST_CableTrayFitting: Når FOB_Sekvensnummer, FOB_Merkestreng eller FOB_Omraade mangler, kjøres C#-forløperen automatisk av Regel 3 før generell utfylling. Den grupperer connector-tilkoblede kabelbroer/fittings og tildeler ett unikt firesifret FOB_Sekvensnummer per gruppe; gruppeplanen kan nummerere selv når hele gruppen mangler eksisterende nummer. Forløperen kan også omnummerere eksisterende grupper for å løse duplikater og lukke sekvensgap. Den behandler alle slike elementer i aktiv modell, ikke bare K5B. Strømskinner, typefunksjonskode STS og FOB_Status S5 utelates/beskyttes. Kontroller modellomfang før kjøring.</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/CableTrayMarkingEngine.cs; CSharpRules/Rule03ParameterFill.cs</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -689,7 +700,7 @@
           <t>Settes alltid til S4</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -702,9 +713,9 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="3" t="n"/>
+    </row>
+    <row r="19" ht="27" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>FOB_Funksjonskode</t>
@@ -715,9 +726,9 @@
           <t>Dette er en type parameter sjekk at verdi verdi KAF er brukt for cable tray og cable tray fittings. For alle conduits og conduits fittings brukes TRR</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
+      <c r="C19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>FOB_Merkesystem</t>
@@ -728,9 +739,9 @@
           <t>Dette er en type parameter sjekk at verdi verdi SPV er brukt for cable tray og cable tray fittings og for alle conduits og conduits fittings</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="C20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="27" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>FOB_System</t>
@@ -741,9 +752,9 @@
           <t>Dette er en type parameter sjekk at verdi verdi 460 er brukt for cable tray og cable tray fittings og for alle conduits og conduits fittings</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
+      <c r="C21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="27" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>PGF_RIE_Alarmsystemer</t>
@@ -754,7 +765,7 @@
           <t>For Fire Alarm Devices synkroniseres instansparameteren fra FOB_FysiskMerke etter regel 9 når verdiene er ulike.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -767,7 +778,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -780,7 +791,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -793,7 +804,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -806,7 +817,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -819,7 +830,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -832,7 +843,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -845,7 +856,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -858,7 +869,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -871,7 +882,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -884,7 +895,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -897,7 +908,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -910,9 +921,9 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35">
+      <c r="C34" s="3" t="n"/>
+    </row>
+    <row r="35" ht="40.5" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>PGF_Mengdetype</t>
@@ -923,7 +934,7 @@
           <t>For rette føringsveier brukes typeparameteren Description sammen med parameteren Size. Den sammensatte teksten kopieres også til tilhørende fittings. For elementer som ikke er føringsveier eller tilhørende fittings, brukes kun typeparameteren Description.</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -936,9 +947,9 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37">
+      <c r="C36" s="3" t="n"/>
+    </row>
+    <row r="37" ht="27" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>PGF_Revisjonsign</t>
@@ -955,7 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="27" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>PGF_Revisjonsindeks</t>
@@ -983,7 +994,7 @@
           <t>Ingen særskilt fagregel angitt</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -996,7 +1007,7 @@
           <t>Settes til dagens dato med format som eksempel 2026.01.10</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/Parameterliste.xlsx
+++ b/config/Parameterliste.xlsx
@@ -697,10 +697,14 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Settes alltid til S4</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n"/>
+          <t>For instanser med eksakt FOB_Entreprise = K5B settes FOB_Status alltid til S4, også når eksisterende verdi er blank, -- eller en annen status. FOB_Status = S5 bevares som lås for kabelbromerking. Andre entrepriseverdier endres ikke.</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/Rule03ParameterFill.cs; rie-bim-agent/rules/regel03-parameterkontroll.md</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">

--- a/config/Parameterliste.xlsx
+++ b/config/Parameterliste.xlsx
@@ -602,16 +602,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="92" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="30" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ns3:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -631,7 +631,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ns3:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -640,16 +640,22 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ns3:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Blank, skrivbar instansverdi fylles K5B av Regel 3. Regel 3 kontrollerer bare eksakt K5B og slike blanke kandidater; andre entrepriseverdier og manglende, dupliserte eller feiltypede enterpriseparametere utelates fra kontroll og rapportering. Eksisterende verdier bevares.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/Rule03ParameterFill.cs; CSharpRules/CableTrayMarkingEngine.cs; CSharpRules/Rule12RevisionParameters.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ns3:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -658,7 +664,7 @@
       </c>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ns3:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -667,7 +673,7 @@
       </c>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ns3:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -676,7 +682,7 @@
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ns3:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -685,7 +691,7 @@
       </c>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ns3:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -694,7 +700,7 @@
       </c>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ns3:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -705,7 +711,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="94.5" ns3:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -716,7 +722,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ns3:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -725,18 +731,20 @@
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="67.5" ns3:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>66</v>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For OST_CableTray og OST_CableTrayFitting beholdes Space-/connectorregelen. For andre K5B-elementer i Regel 3: Ved blank FOB_Omraade eller -- kopieres nærmeste gyldige instansverdi med samme FOB_Entreprise=K5B og FOB_Leveransepakke, men annen familie. Primærsøk 50–1500 mm; fallback 1500–3000 mm bare uten primærtreff. Hvis ingen kandidat finnes innen 3000 mm, fortsetter K5B-søket uten øvre avstandsgrense til nærmeste gyldige kandidat. Motstridende kilder innen 1 mm, manglende identitet eller ingen kandidat noe sted gir ingen skriving og logges uavklart. Bevar gyldige verdier.</t>
+        </is>
       </c>
       <c r="C13" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ns3:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
@@ -745,7 +753,7 @@
       </c>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="27" customHeight="1" ns3:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
@@ -756,7 +764,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="94.5" ns3:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
@@ -767,7 +775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="40.5" ns3:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
@@ -778,7 +786,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ns3:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -787,7 +795,7 @@
       </c>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="27" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>35</v>
       </c>
@@ -796,7 +804,7 @@
       </c>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="27" customHeight="1" ns3:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>37</v>
       </c>
@@ -805,7 +813,7 @@
       </c>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="27" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>39</v>
       </c>
@@ -814,16 +822,22 @@
       </c>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="27" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>På OST_FireAlarmDevices synkroniseres fra FOB_FysiskMerke etter Regel 9. I andre kategorier gjelder Regel 3s generelle utfylling; blank verdi fylles med --.</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/Rule09SyncAlarmSystemMark.cs; CSharpRules/Rule03ParameterFill.cs; rie-bim-agent/rules/regel03-parameterkontroll.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ns3:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>43</v>
       </c>
@@ -832,7 +846,7 @@
       </c>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ns3:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
@@ -841,16 +855,22 @@
       </c>
       <c r="C24" s="3"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ns3:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>For alle instanser i Regel 3-utvalget der parameteren finnes skal verdien være nøyaktig --. Overskriv blanke og alle andre verdier.</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Regel 3 og Regel 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ns3:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>46</v>
       </c>
@@ -859,7 +879,7 @@
       </c>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ns3:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>47</v>
       </c>
@@ -868,16 +888,22 @@
       </c>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ns3:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Gjelder kun trekkerør (OST_Conduit) og tilhørende fittings (OST_ConduitFitting). Bruk Regel 3s vanlige utfylling etter parameterlisten; blank verdi settes til --. Andre kategorier kontrolleres, fylles eller rapporteres ikke.</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/Rule03ParameterFill.cs; CSharpRules/Rule12RevisionParameters.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ns3:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>49</v>
       </c>
@@ -886,7 +912,7 @@
       </c>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ns3:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>50</v>
       </c>
@@ -895,7 +921,7 @@
       </c>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" s="4" customFormat="1" ns3:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>63</v>
       </c>
@@ -906,7 +932,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ns3:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>51</v>
       </c>
@@ -915,7 +941,7 @@
       </c>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ns3:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>52</v>
       </c>
@@ -924,16 +950,22 @@
       </c>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ns3:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Gjelder kun trekkerør (OST_Conduit) og tilhørende fittings (OST_ConduitFitting). Bruk Regel 3s vanlige utfylling etter parameterlisten; blank verdi settes til --. Andre kategorier kontrolleres, fylles eller rapporteres ikke.</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/Rule03ParameterFill.cs; CSharpRules/Rule12RevisionParameters.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ns3:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>54</v>
       </c>
@@ -942,7 +974,7 @@
       </c>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="40.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>55</v>
       </c>
@@ -951,18 +983,20 @@
       </c>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="1:3" ht="54" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="54" ns3:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>67</v>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ved blank PGF_PNS eller -- kopieres nærmeste gyldige instansverdi med samme FOB_Entreprise=K5B og FOB_Leveransepakke, men annen familie. Primærsøk 50–1500 mm; fallback 1500–3000 mm bare uten primærtreff. Hvis ingen kandidat finnes innen 3000 mm, fortsetter K5B-søket uten øvre avstandsgrense til nærmeste gyldige kandidat. Motstridende kilder innen 1 mm, manglende identitet eller ingen kandidat noe sted gir ingen skriving og logges uavklart. Bevar gyldige verdier.</t>
+        </is>
       </c>
       <c r="C37" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="27" customHeight="1" ns3:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>58</v>
       </c>
@@ -973,7 +1007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="27" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>59</v>
       </c>
@@ -984,7 +1018,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ns3:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>60</v>
       </c>
@@ -993,7 +1027,7 @@
       </c>
       <c r="C40" s="3"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ns3:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>61</v>
       </c>

--- a/config/Parameterliste.xlsx
+++ b/config/Parameterliste.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">For OST_CableTray og OST_CableTrayFitting beholdes Space-/connectorregelen. For andre K5B-elementer i Regel 3: Ved blank FOB_Omraade eller -- kopieres nærmeste gyldige instansverdi med samme FOB_Entreprise=K5B og FOB_Leveransepakke, men annen familie. Primærsøk 50–1500 mm; fallback 1500–3000 mm bare uten primærtreff. Hvis ingen kandidat finnes innen 3000 mm, fortsetter K5B-søket uten øvre avstandsgrense til nærmeste gyldige kandidat. Motstridende kilder innen 1 mm, manglende identitet eller ingen kandidat noe sted gir ingen skriving og logges uavklart. Bevar gyldige verdier.</t>
+          <t xml:space="preserve">For OST_CableTray og OST_CableTrayFitting beholdes Space-/connectorregelen. For andre K5B-elementer i Regel 3: Ved blank FOB_Omraade, -- eller .. (.. tolkes som tomt og er ikke gyldig kilde) kopieres nærmeste gyldige instansverdi med samme FOB_Entreprise=K5B og FOB_Leveransepakke, men annen familie. Primærsøk 50–1500 mm; fallback 1500–3000 mm bare uten primærtreff. Hvis ingen kandidat finnes innen 3000 mm, fortsetter K5B-søket uten øvre avstandsgrense til nærmeste gyldige kandidat. Motstridende kilder innen 1 mm, manglende identitet eller ingen kandidat noe sted gir ingen skriving og logges uavklart. Bevar gyldige verdier.</t>
         </is>
       </c>
       <c r="C13" s="3" t="s">
@@ -989,7 +989,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved blank PGF_PNS eller -- kopieres nærmeste gyldige instansverdi med samme FOB_Entreprise=K5B og FOB_Leveransepakke, men annen familie. Primærsøk 50–1500 mm; fallback 1500–3000 mm bare uten primærtreff. Hvis ingen kandidat finnes innen 3000 mm, fortsetter K5B-søket uten øvre avstandsgrense til nærmeste gyldige kandidat. Motstridende kilder innen 1 mm, manglende identitet eller ingen kandidat noe sted gir ingen skriving og logges uavklart. Bevar gyldige verdier.</t>
+          <t xml:space="preserve">Ved blank, -- eller .. i PGF_PNS (.. tolkes som tomt og er ikke gyldig kilde) kopieres nærmeste gyldige instansverdi med samme FOB_Entreprise=K5B og FOB_Leveransepakke, men annen familie. Primærsøk 50–1500 mm; fallback 1500–3000 mm bare uten primærtreff. Hvis ingen kandidat finnes innen 3000 mm, fortsetter K5B-søket uten øvre avstandsgrense til nærmeste gyldige kandidat. Motstridende kilder innen 1 mm, manglende identitet eller ingen kandidat noe sted gir ingen skriving og logges uavklart. Bevar gyldige verdier.</t>
         </is>
       </c>
       <c r="C37" s="3" t="s">

--- a/config/Parameterliste.xlsx
+++ b/config/Parameterliste.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Gjelder kun trekkerør (OST_Conduit) og tilhørende fittings (OST_ConduitFitting). Bruk Regel 3s vanlige utfylling etter parameterlisten; blank verdi settes til --. Andre kategorier kontrolleres, fylles eller rapporteres ikke.</t>
+          <t>Gjelder alle elektrofamiliekategorier i Regel 3-utvalget der parameteren finnes som instansparameter. For tom eller bare whitespace-verdi skal Regel 3 skrive nøyaktig '--'. Bevar eksisterende verdier. Ikke bruk typeparameterfallback eller opprett manglende parametere.</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Gjelder kun trekkerør (OST_Conduit) og tilhørende fittings (OST_ConduitFitting). Bruk Regel 3s vanlige utfylling etter parameterlisten; blank verdi settes til --. Andre kategorier kontrolleres, fylles eller rapporteres ikke.</t>
+          <t>Gjelder alle elektrofamiliekategorier i Regel 3-utvalget der parameteren finnes som instansparameter. For tom eller bare whitespace-verdi skal Regel 3 skrive nøyaktig '--'. Bevar eksisterende verdier. Ikke bruk typeparameterfallback eller opprett manglende parametere.</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">

--- a/config/Parameterliste.xlsx
+++ b/config/Parameterliste.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>CSharpRules/Rule03ParameterFill.cs; CSharpRules/CableTrayMarkingEngine.cs; CSharpRules/Rule12RevisionParameters.cs</t>
+          <t>CSharpRules/Rule03ParameterFill.cs; CSharpRules/CableTrayMarkingEngine.cs</t>
         </is>
       </c>
     </row>
@@ -757,11 +757,15 @@
       <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>28</v>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Regel 3 kontrollerer kun utfylling av tekst-instansparameteren. Tom tekst, bare whitespace og -- etter trimming er ugyldig. Manglende, duplisert eller feiltypet parameter rapporteres. Ingen automatisk utfylling, kopiering, korrigering eller Excel-revisjonsoppslag. Kontrollen er uavhengig av leveransepakke.</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/Rule03ParameterFill.cs; rie-bim-agent/parameter-rules/revision-rules.md</t>
+        </is>
       </c>
     </row>
     <row r="16" spans="1:3" ht="94.5" ns3:dyDescent="0.25">
@@ -899,7 +903,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>CSharpRules/Rule03ParameterFill.cs; CSharpRules/Rule12RevisionParameters.cs</t>
+          <t>CSharpRules/Rule03ParameterFill.cs</t>
         </is>
       </c>
     </row>
@@ -961,7 +965,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>CSharpRules/Rule03ParameterFill.cs; CSharpRules/Rule12RevisionParameters.cs</t>
+          <t>CSharpRules/Rule03ParameterFill.cs</t>
         </is>
       </c>
     </row>
@@ -1000,22 +1004,30 @@
       <c r="A38" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>28</v>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Regel 3 kontrollerer kun utfylling av tekst-instansparameteren. Tom tekst, bare whitespace og -- etter trimming er ugyldig. Manglende, duplisert eller feiltypet parameter rapporteres. Ingen automatisk utfylling, kopiering, korrigering eller Excel-revisjonsoppslag. Kontrollen er uavhengig av leveransepakke.</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/Rule03ParameterFill.cs; rie-bim-agent/parameter-rules/revision-rules.md</t>
+        </is>
       </c>
     </row>
     <row r="39" spans="1:3" ht="27" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>28</v>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Regel 3 kontrollerer kun utfylling av tekst-instansparameteren. Tom tekst, bare whitespace og -- etter trimming er ugyldig. Manglende, duplisert eller feiltypet parameter rapporteres. Ingen automatisk utfylling, kopiering, korrigering eller Excel-revisjonsoppslag. Kontrollen er uavhengig av leveransepakke.</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>CSharpRules/Rule03ParameterFill.cs; rie-bim-agent/parameter-rules/revision-rules.md</t>
+        </is>
       </c>
     </row>
     <row r="40" spans="1:3" ns3:dyDescent="0.25">

--- a/config/Parameterliste.xlsx
+++ b/config/Parameterliste.xlsx
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>For OST_CableTray, OST_CableTrayFitting, OST_Conduit og OST_ConduitFitting, samt instanser der én tekst-instansparameter FOB_Eksistensstatus har nøyaktig verdien Infoelement, settes en entydig, skrivbar tekst-instansparameter til nøyaktig --. Ingen rom-, nærhets- eller føringsveikilder brukes. For øvrige instanser i Regel 3-scope fylles romverdien ikke automatisk; blank, --, manglende, duplisert eller feiltypet parameter flagges i Romkontroll. Manglende, dupliserte, feiltypede eller skrivebeskyttede målparametere flagges uten skriving.</t>
+          <t>For OST_Conduit og OST_ConduitFitting, samt instanser der én tekst-instansparameter FOB_Eksistensstatus har nøyaktig verdien Infoelement, settes en entydig, skrivbar tekst-instansparameter til nøyaktig --. For OST_CableTray og OST_CableTrayFitting setter Regel 3 ikke romnummer til --; eksisterende verdier bevares, og blank eller -- flagges i Romkontroll. Manglende romnummer etter dRofus-synk fylles separat fra samme dokumenterte strekk sin representant. For øvrige instanser i Regel 3-scope fylles romverdien ikke automatisk; blank, --, manglende, duplisert eller feiltypet parameter flagges i Romkontroll. Manglende, dupliserte, feiltypede eller skrivebeskyttede målparametere flagges uten skriving.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
